--- a/app/config/assets/framework/forms/framework/framework.xlsx
+++ b/app/config/assets/framework/forms/framework/framework.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clarice\cold-chain\cold-chain-app-designer\app\config\assets\framework\forms\framework\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Projects\ODK-X\our-work\app\config\assets\framework\forms\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D668DA8-2784-44BB-8D65-3BC89D675A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7644" windowHeight="144" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,23 @@
     <sheet name="framework_translations" sheetId="5" r:id="rId5"/>
     <sheet name="common_translations" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1194">
   <si>
     <t>comments</t>
   </si>
@@ -1982,9 +1994,6 @@
     <t>add_sentinel_survey</t>
   </si>
   <si>
-    <t>Add Sentinel Survey</t>
-  </si>
-  <si>
     <t>Añadir Encuesta Centinela</t>
   </si>
   <si>
@@ -3572,11 +3581,131 @@
   <si>
     <t>Días con temperatura inferior a 2°C, últimos 30 días</t>
   </si>
+  <si>
+    <t>Add Sentinel Survey</t>
+  </si>
+  <si>
+    <t>add_followup_survey</t>
+  </si>
+  <si>
+    <t>view_tfa_survey</t>
+  </si>
+  <si>
+    <t>view_followup_survey</t>
+  </si>
+  <si>
+    <t>add_tfa_survey</t>
+  </si>
+  <si>
+    <t>Add Follow-up Survey</t>
+  </si>
+  <si>
+    <t>View All Follow-up Surveys</t>
+  </si>
+  <si>
+    <t>Add TFA Survey</t>
+  </si>
+  <si>
+    <t>View All TFA Surveys</t>
+  </si>
+  <si>
+    <t>followup_data_deleted_successfully</t>
+  </si>
+  <si>
+    <t>are_you_sure_you_want_to_delete_this_followup_survey</t>
+  </si>
+  <si>
+    <t>followup_survey_information</t>
+  </si>
+  <si>
+    <t>edit_followup_survey</t>
+  </si>
+  <si>
+    <t>delete_followup_survey</t>
+  </si>
+  <si>
+    <t>Edit Follow-up Survey</t>
+  </si>
+  <si>
+    <t>Delete Follow-up Survey</t>
+  </si>
+  <si>
+    <t>tfa_data_deleted_successfully</t>
+  </si>
+  <si>
+    <t>are_you_sure_you_want_to_delete_this_tfa_survey</t>
+  </si>
+  <si>
+    <t>tfa_survey_information</t>
+  </si>
+  <si>
+    <t>edit_tfa_survey</t>
+  </si>
+  <si>
+    <t>delete_tfa_survey</t>
+  </si>
+  <si>
+    <t>TFA data deleted successfully</t>
+  </si>
+  <si>
+    <t>Follow-up data deleted successfully</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete this Follow-up survey?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete this TFA survey?</t>
+  </si>
+  <si>
+    <t>Edit TFA Survey</t>
+  </si>
+  <si>
+    <t>Delete TFA Survey</t>
+  </si>
+  <si>
+    <t>date_no_colon</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>followup_date</t>
+  </si>
+  <si>
+    <t>followup_id</t>
+  </si>
+  <si>
+    <t>Follow-up Date:</t>
+  </si>
+  <si>
+    <t>Follow-up ID:</t>
+  </si>
+  <si>
+    <t>Basic Follow-up Survey Information</t>
+  </si>
+  <si>
+    <t>Basic TFA Survey Information</t>
+  </si>
+  <si>
+    <t>TFA Date:</t>
+  </si>
+  <si>
+    <t>TFA ID:</t>
+  </si>
+  <si>
+    <t>tfa_date</t>
+  </si>
+  <si>
+    <t>tfa_id</t>
+  </si>
+  <si>
+    <t>New Failure</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10">
     <font>
       <sz val="10"/>
@@ -3639,6 +3768,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3699,82 +3829,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3782,12 +3866,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4164,13 +4242,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="26.77734375" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="1025" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="3" max="1025" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4198,22 +4276,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I87"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="101.21875" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" customWidth="1"/>
-    <col min="4" max="4" width="46.21875" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="2" max="2" width="101.1796875" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
+    <col min="4" max="4" width="46.1796875" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="21.77734375" customWidth="1"/>
-    <col min="8" max="8" width="31.44140625" customWidth="1"/>
-    <col min="9" max="9" width="22.21875" customWidth="1"/>
-    <col min="10" max="1025" width="17.21875" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" customWidth="1"/>
+    <col min="8" max="8" width="31.453125" customWidth="1"/>
+    <col min="9" max="9" width="22.1796875" customWidth="1"/>
+    <col min="10" max="1025" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.55" customHeight="1">
+    <row r="1" spans="1:9" ht="17.5" customHeight="1">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -4240,193 +4318,193 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="C2" s="14" t="s">
+    <row r="2" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="C2" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="17.5" customHeight="1">
+      <c r="E3" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="I2" s="15"/>
-    </row>
-    <row r="3" spans="1:9" s="14" customFormat="1" ht="17.55" customHeight="1">
-      <c r="E3" s="14" t="s">
+      <c r="F3" t="s">
         <v>633</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="G3" s="14" t="s">
+    </row>
+    <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="C4" s="3" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="C4" s="14" t="s">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" ht="41.25" customHeight="1">
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="1:9" s="14" customFormat="1" ht="41.25" customHeight="1">
-      <c r="E5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="H5" s="14" t="s">
+    </row>
+    <row r="6" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="C6" s="3" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="C6" s="14" t="s">
+    <row r="7" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="C7" s="3" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="C7" s="14" t="s">
+    <row r="8" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B8"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="59.25" customHeight="1">
+      <c r="A9"/>
+      <c r="B9" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>643</v>
-      </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="9" spans="1:9" s="14" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17" t="s">
-        <v>644</v>
-      </c>
-      <c r="E9" s="14" t="s">
+      <c r="G9" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="14" t="s">
+    </row>
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10" s="3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>606</v>
+      </c>
+      <c r="B11"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" ht="59.25" customHeight="1">
+      <c r="A12"/>
+      <c r="B12" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A11" s="16" t="s">
-        <v>606</v>
-      </c>
-      <c r="B11" s="16"/>
-    </row>
-    <row r="12" spans="1:9" s="14" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
-        <v>687</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="G12" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="14" t="s">
+    </row>
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13" s="3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>688</v>
+      </c>
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="59.25" customHeight="1">
+      <c r="A15"/>
+      <c r="B15" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A14" s="16" t="s">
-        <v>689</v>
-      </c>
-      <c r="B14" s="16"/>
-    </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17" t="s">
-        <v>690</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="G15" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="14" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="17" ht="17.55" customHeight="1"/>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16" s="3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="17" ht="17.5" customHeight="1"/>
     <row r="18" ht="59.25" customHeight="1"/>
     <row r="19" ht="17.25" customHeight="1"/>
-    <row r="20" ht="17.55" customHeight="1"/>
+    <row r="20" ht="17.5" customHeight="1"/>
     <row r="21" ht="66" customHeight="1"/>
     <row r="22" ht="17.25" customHeight="1"/>
-    <row r="23" ht="17.55" customHeight="1"/>
+    <row r="23" ht="17.5" customHeight="1"/>
     <row r="24" ht="66" customHeight="1"/>
     <row r="25" ht="17.25" customHeight="1"/>
-    <row r="26" ht="17.55" customHeight="1"/>
+    <row r="26" ht="17.5" customHeight="1"/>
     <row r="27" ht="66" customHeight="1"/>
     <row r="28" ht="17.25" customHeight="1"/>
-    <row r="29" ht="17.55" customHeight="1"/>
+    <row r="29" ht="17.5" customHeight="1"/>
     <row r="30" ht="66" customHeight="1"/>
     <row r="31" ht="17.25" customHeight="1"/>
-    <row r="32" ht="17.55" customHeight="1"/>
+    <row r="32" ht="17.5" customHeight="1"/>
     <row r="33" ht="66" customHeight="1"/>
     <row r="34" ht="17.25" customHeight="1"/>
-    <row r="35" ht="17.55" customHeight="1"/>
+    <row r="35" ht="17.5" customHeight="1"/>
     <row r="36" ht="66" customHeight="1"/>
     <row r="37" ht="17.25" customHeight="1"/>
-    <row r="38" ht="17.55" customHeight="1"/>
+    <row r="38" ht="17.5" customHeight="1"/>
     <row r="39" ht="66" customHeight="1"/>
     <row r="40" ht="17.25" customHeight="1"/>
-    <row r="41" ht="17.55" customHeight="1"/>
+    <row r="41" ht="17.5" customHeight="1"/>
     <row r="42" ht="66" customHeight="1"/>
     <row r="43" ht="17.25" customHeight="1"/>
-    <row r="44" ht="17.55" customHeight="1"/>
+    <row r="44" ht="17.5" customHeight="1"/>
     <row r="45" ht="66" customHeight="1"/>
     <row r="46" ht="17.25" customHeight="1"/>
-    <row r="47" ht="17.55" customHeight="1"/>
+    <row r="47" ht="17.5" customHeight="1"/>
     <row r="48" ht="66" customHeight="1"/>
     <row r="49" ht="17.25" customHeight="1"/>
-    <row r="50" ht="17.55" customHeight="1"/>
+    <row r="50" ht="17.5" customHeight="1"/>
     <row r="51" ht="66" customHeight="1"/>
     <row r="52" ht="17.25" customHeight="1"/>
-    <row r="53" ht="17.55" customHeight="1"/>
+    <row r="53" ht="17.5" customHeight="1"/>
     <row r="54" ht="66" customHeight="1"/>
     <row r="55" ht="17.25" customHeight="1"/>
-    <row r="56" ht="17.55" customHeight="1"/>
+    <row r="56" ht="17.5" customHeight="1"/>
     <row r="57" ht="66" customHeight="1"/>
     <row r="58" ht="17.25" customHeight="1"/>
-    <row r="59" ht="17.55" customHeight="1"/>
+    <row r="59" ht="17.5" customHeight="1"/>
     <row r="60" ht="66" customHeight="1"/>
     <row r="61" ht="17.25" customHeight="1"/>
-    <row r="62" ht="17.55" customHeight="1"/>
+    <row r="62" ht="17.5" customHeight="1"/>
     <row r="63" ht="66" customHeight="1"/>
     <row r="64" ht="17.25" customHeight="1"/>
-    <row r="65" ht="17.55" customHeight="1"/>
+    <row r="65" ht="17.5" customHeight="1"/>
     <row r="66" ht="66" customHeight="1"/>
     <row r="67" ht="17.25" customHeight="1"/>
-    <row r="68" ht="17.55" customHeight="1"/>
+    <row r="68" ht="17.5" customHeight="1"/>
     <row r="69" ht="66" customHeight="1"/>
     <row r="70" ht="17.25" customHeight="1"/>
-    <row r="71" ht="17.55" customHeight="1"/>
+    <row r="71" ht="17.5" customHeight="1"/>
     <row r="72" ht="66" customHeight="1"/>
-    <row r="73" ht="17.100000000000001" customHeight="1"/>
-    <row r="75" ht="62.1" customHeight="1"/>
-    <row r="78" ht="62.1" customHeight="1"/>
+    <row r="73" ht="17" customHeight="1"/>
+    <row r="75" ht="62" customHeight="1"/>
+    <row r="78" ht="62" customHeight="1"/>
     <row r="80" ht="12" customHeight="1"/>
-    <row r="81" ht="58.05" customHeight="1"/>
+    <row r="81" ht="58" customHeight="1"/>
     <row r="83" ht="12" customHeight="1"/>
-    <row r="84" ht="58.05" customHeight="1"/>
+    <row r="84" ht="58" customHeight="1"/>
     <row r="86" ht="12" customHeight="1"/>
-    <row r="87" ht="58.05" customHeight="1"/>
+    <row r="87" ht="58" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4439,17 +4517,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="17.21875" customWidth="1"/>
-    <col min="3" max="4" width="24.77734375" customWidth="1"/>
-    <col min="5" max="5" width="24.77734375" style="24" customWidth="1"/>
-    <col min="6" max="7" width="24.77734375" customWidth="1"/>
-    <col min="8" max="8" width="24.77734375" style="24" customWidth="1"/>
-    <col min="9" max="9" width="41.21875" customWidth="1"/>
-    <col min="10" max="1027" width="17.21875" customWidth="1"/>
+    <col min="1" max="2" width="17.1796875" customWidth="1"/>
+    <col min="3" max="8" width="24.81640625" customWidth="1"/>
+    <col min="9" max="9" width="41.1796875" customWidth="1"/>
+    <col min="10" max="1027" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" customHeight="1">
@@ -4465,8 +4540,8 @@
       <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="37" t="s">
-        <v>915</v>
+      <c r="E1" s="1" t="s">
+        <v>914</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
@@ -4474,8 +4549,8 @@
       <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="36" t="s">
-        <v>914</v>
+      <c r="H1" s="8" t="s">
+        <v>913</v>
       </c>
       <c r="I1" t="s">
         <v>0</v>
@@ -4493,10 +4568,10 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="25"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4507,10 +4582,10 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="25"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="25"/>
+      <c r="H3" s="1"/>
       <c r="I3" t="s">
         <v>21</v>
       </c>
@@ -4526,7 +4601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.05" customHeight="1">
+    <row r="5" spans="1:10" ht="28" customHeight="1">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -4536,8 +4611,8 @@
       <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="38" t="s">
-        <v>916</v>
+      <c r="E5" t="s">
+        <v>915</v>
       </c>
       <c r="I5" t="s">
         <v>27</v>
@@ -4557,8 +4632,8 @@
       <c r="G7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="39" t="s">
-        <v>917</v>
+      <c r="H7" s="8" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
@@ -4571,23 +4646,22 @@
       <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A9" t="s">
+        <v>855</v>
+      </c>
+      <c r="F9" t="s">
+        <v>856</v>
+      </c>
+      <c r="G9" t="s">
+        <v>912</v>
+      </c>
+      <c r="H9" t="s">
         <v>918</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="18" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A9" s="18" t="s">
-        <v>856</v>
-      </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="18" t="s">
-        <v>857</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>913</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="18.75" customHeight="1">
@@ -4597,10 +4671,10 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="25"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="25"/>
+      <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="12" spans="1:10" ht="18.75" customHeight="1"/>
@@ -4612,14 +4686,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="31.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="1025" width="8.77734375" customWidth="1"/>
+    <col min="4" max="1025" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4635,35 +4709,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>634</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>645</v>
+        <v>633</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>634</v>
-      </c>
-      <c r="B3" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17.5" customHeight="1">
+      <c r="A4" t="s">
+        <v>633</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="17.55" customHeight="1">
-      <c r="A4" t="s">
-        <v>634</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>691</v>
+      <c r="C4" s="3" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -4678,18 +4752,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D198"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="49.77734375" customWidth="1"/>
-    <col min="2" max="2" width="52.21875" customWidth="1"/>
-    <col min="3" max="3" width="33.21875" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" customWidth="1"/>
-    <col min="5" max="1025" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="49.81640625" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" customWidth="1"/>
+    <col min="3" max="3" width="33.1796875" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" customWidth="1"/>
+    <col min="5" max="1025" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.05" customHeight="1">
+    <row r="1" spans="1:4" ht="13" customHeight="1">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -4699,11 +4773,11 @@
       <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="13.05" customHeight="1">
+      <c r="D1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13" customHeight="1">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -4713,11 +4787,11 @@
       <c r="C2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="29" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="13.05" customHeight="1">
+      <c r="D2" s="8" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="13" customHeight="1">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -4727,11 +4801,11 @@
       <c r="C3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="29" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="13.05" customHeight="1">
+      <c r="D3" s="8" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13" customHeight="1">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -4741,11 +4815,11 @@
       <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="13.05" customHeight="1">
+      <c r="D4" s="8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13" customHeight="1">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -4755,11 +4829,11 @@
       <c r="C5" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="13.05" customHeight="1">
+      <c r="D5" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13" customHeight="1">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -4769,8 +4843,8 @@
       <c r="C6" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>862</v>
+      <c r="D6" s="5" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4783,8 +4857,8 @@
       <c r="C7" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>863</v>
+      <c r="D7" s="8" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4797,8 +4871,8 @@
       <c r="C8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>799</v>
+      <c r="D8" s="8" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4811,8 +4885,8 @@
       <c r="C9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>800</v>
+      <c r="D9" s="8" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4825,11 +4899,11 @@
       <c r="C10" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="13.8" customHeight="1">
+      <c r="D10" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13.75" customHeight="1">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -4839,11 +4913,11 @@
       <c r="C11" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="13.8" customHeight="1">
+      <c r="D11" s="8" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13.75" customHeight="1">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -4853,8 +4927,8 @@
       <c r="C12" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="29" t="s">
-        <v>866</v>
+      <c r="D12" s="8" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4867,8 +4941,8 @@
       <c r="C13" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>867</v>
+      <c r="D13" s="8" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4881,8 +4955,8 @@
       <c r="C14" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>868</v>
+      <c r="D14" s="14" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4895,8 +4969,8 @@
       <c r="C15" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>869</v>
+      <c r="D15" s="14" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4909,8 +4983,8 @@
       <c r="C16" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>870</v>
+      <c r="D16" s="14" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4923,8 +4997,8 @@
       <c r="C17" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>871</v>
+      <c r="D17" s="14" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4937,8 +5011,8 @@
       <c r="C18" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="29" t="s">
-        <v>872</v>
+      <c r="D18" s="8" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4951,8 +5025,8 @@
       <c r="C19" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="29" t="s">
-        <v>873</v>
+      <c r="D19" s="8" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4965,8 +5039,8 @@
       <c r="C20" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>874</v>
+      <c r="D20" s="8" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4979,8 +5053,8 @@
       <c r="C21" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>875</v>
+      <c r="D21" s="8" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4993,8 +5067,8 @@
       <c r="C22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="29" t="s">
-        <v>876</v>
+      <c r="D22" s="8" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5007,8 +5081,8 @@
       <c r="C23" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="29" t="s">
-        <v>877</v>
+      <c r="D23" s="8" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5021,8 +5095,8 @@
       <c r="C24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="29" t="s">
-        <v>878</v>
+      <c r="D24" s="8" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5035,8 +5109,8 @@
       <c r="C25" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>879</v>
+      <c r="D25" s="8" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5049,8 +5123,8 @@
       <c r="C26" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="29" t="s">
-        <v>880</v>
+      <c r="D26" s="8" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5063,11 +5137,11 @@
       <c r="C27" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="29" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="28.35" customHeight="1">
+      <c r="D27" s="8" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.25" customHeight="1">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -5077,8 +5151,8 @@
       <c r="C28" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="35" t="s">
-        <v>882</v>
+      <c r="D28" s="15" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5091,7 +5165,6 @@
       <c r="C29" t="s">
         <v>122</v>
       </c>
-      <c r="D29" s="24"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
@@ -5103,8 +5176,8 @@
       <c r="C30" t="s">
         <v>125</v>
       </c>
-      <c r="D30" s="29" t="s">
-        <v>883</v>
+      <c r="D30" s="8" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5117,8 +5190,8 @@
       <c r="C31" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="29" t="s">
-        <v>884</v>
+      <c r="D31" s="8" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5131,8 +5204,8 @@
       <c r="C33" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="28" t="s">
-        <v>885</v>
+      <c r="D33" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5145,8 +5218,8 @@
       <c r="C34" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="28" t="s">
-        <v>886</v>
+      <c r="D34" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5159,11 +5232,11 @@
       <c r="C35" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="28" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="250.8">
+      <c r="D35" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="237.5">
       <c r="A36" t="s">
         <v>138</v>
       </c>
@@ -5173,8 +5246,8 @@
       <c r="C36" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D36" s="35" t="s">
-        <v>888</v>
+      <c r="D36" s="15" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5187,8 +5260,8 @@
       <c r="C37" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="29" t="s">
-        <v>889</v>
+      <c r="D37" s="8" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5201,8 +5274,8 @@
       <c r="C38" t="s">
         <v>146</v>
       </c>
-      <c r="D38" s="29" t="s">
-        <v>890</v>
+      <c r="D38" s="8" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5215,8 +5288,8 @@
       <c r="C39" t="s">
         <v>149</v>
       </c>
-      <c r="D39" s="28" t="s">
-        <v>891</v>
+      <c r="D39" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5229,8 +5302,8 @@
       <c r="C40" t="s">
         <v>152</v>
       </c>
-      <c r="D40" s="28" t="s">
-        <v>892</v>
+      <c r="D40" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5243,8 +5316,8 @@
       <c r="C41" t="s">
         <v>155</v>
       </c>
-      <c r="D41" s="28" t="s">
-        <v>893</v>
+      <c r="D41" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5257,8 +5330,8 @@
       <c r="C42" t="s">
         <v>158</v>
       </c>
-      <c r="D42" s="28" t="s">
-        <v>894</v>
+      <c r="D42" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -5271,7 +5344,7 @@
       <c r="C43" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" t="s">
         <v>160</v>
       </c>
     </row>
@@ -5285,8 +5358,8 @@
       <c r="C44" t="s">
         <v>163</v>
       </c>
-      <c r="D44" s="28" t="s">
-        <v>895</v>
+      <c r="D44" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -5299,8 +5372,8 @@
       <c r="C45" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="28" t="s">
-        <v>896</v>
+      <c r="D45" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5313,8 +5386,8 @@
       <c r="C46" t="s">
         <v>169</v>
       </c>
-      <c r="D46" s="28" t="s">
-        <v>897</v>
+      <c r="D46" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5322,13 +5395,13 @@
         <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>1193</v>
       </c>
       <c r="C47" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="28" t="s">
-        <v>898</v>
+      <c r="D47" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -5341,8 +5414,8 @@
       <c r="C48" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="28" t="s">
-        <v>899</v>
+      <c r="D48" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -5355,11 +5428,11 @@
       <c r="C49" t="s">
         <v>178</v>
       </c>
-      <c r="D49" s="33" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="13.05" customHeight="1">
+      <c r="D49" s="13" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="13" customHeight="1">
       <c r="A50" t="s">
         <v>179</v>
       </c>
@@ -5369,8 +5442,8 @@
       <c r="C50" t="s">
         <v>181</v>
       </c>
-      <c r="D50" s="33" t="s">
-        <v>901</v>
+      <c r="D50" s="13" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -5383,8 +5456,8 @@
       <c r="C51" t="s">
         <v>184</v>
       </c>
-      <c r="D51" s="28" t="s">
-        <v>902</v>
+      <c r="D51" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -5397,8 +5470,8 @@
       <c r="C52" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="28" t="s">
-        <v>884</v>
+      <c r="D52" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -5411,7 +5484,7 @@
       <c r="C53" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="D53" s="13" t="s">
         <v>187</v>
       </c>
     </row>
@@ -5425,8 +5498,8 @@
       <c r="C54" t="s">
         <v>172</v>
       </c>
-      <c r="D54" s="33" t="s">
-        <v>898</v>
+      <c r="D54" s="13" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -5439,8 +5512,8 @@
       <c r="C55" t="s">
         <v>192</v>
       </c>
-      <c r="D55" s="33" t="s">
-        <v>903</v>
+      <c r="D55" s="13" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -5453,8 +5526,8 @@
       <c r="C56" t="s">
         <v>195</v>
       </c>
-      <c r="D56" s="33" t="s">
-        <v>904</v>
+      <c r="D56" s="13" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -5467,106 +5540,106 @@
       <c r="C57" t="s">
         <v>198</v>
       </c>
-      <c r="D57" s="33" t="s">
+      <c r="D57" s="13" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" s="3" customFormat="1">
+      <c r="A58" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="58" spans="1:4" s="6" customFormat="1">
-      <c r="A58" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="D58" s="26" t="s">
+    <row r="59" spans="1:4" s="3" customFormat="1">
+      <c r="A59" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="59" spans="1:4" s="6" customFormat="1">
-      <c r="A59" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="D59" s="26" t="s">
+    <row r="60" spans="1:4" s="3" customFormat="1" ht="37.5">
+      <c r="A60" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="60" spans="1:4" s="6" customFormat="1" ht="39.6">
-      <c r="A60" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>621</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="D60" s="26" t="s">
+    <row r="61" spans="1:4" s="3" customFormat="1" ht="25">
+      <c r="A61" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="61" spans="1:4" s="6" customFormat="1" ht="26.4">
-      <c r="A61" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>626</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" s="6" customFormat="1">
-      <c r="A62" s="8" t="s">
+    <row r="62" spans="1:4" s="3" customFormat="1">
+      <c r="A62" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="3" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" s="3" customFormat="1">
+      <c r="A63" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="63" spans="1:4" s="6" customFormat="1">
-      <c r="A63" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="26.4">
+    <row r="64" spans="1:4" ht="25">
       <c r="A64" t="s">
         <v>199</v>
       </c>
       <c r="B64" t="s">
         <v>200</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D64" s="26" t="s">
-        <v>722</v>
+      <c r="D64" s="5" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -5576,11 +5649,11 @@
       <c r="B65" t="s">
         <v>202</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D65" s="26" t="s">
-        <v>723</v>
+      <c r="D65" s="5" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -5590,11 +5663,11 @@
       <c r="B66" t="s">
         <v>205</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="D66" s="26" t="s">
-        <v>910</v>
+      <c r="D66" s="5" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -5604,11 +5677,11 @@
       <c r="B67" t="s">
         <v>208</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D67" s="26" t="s">
-        <v>726</v>
+      <c r="D67" s="5" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -5621,8 +5694,8 @@
       <c r="C68" t="s">
         <v>210</v>
       </c>
-      <c r="D68" s="26" t="s">
-        <v>727</v>
+      <c r="D68" s="5" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -5635,8 +5708,8 @@
       <c r="C69" t="s">
         <v>215</v>
       </c>
-      <c r="D69" s="26" t="s">
-        <v>729</v>
+      <c r="D69" s="5" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -5646,11 +5719,11 @@
       <c r="B70" t="s">
         <v>217</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D70" s="26" t="s">
-        <v>730</v>
+      <c r="D70" s="5" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -5660,28 +5733,28 @@
       <c r="B71" t="s">
         <v>220</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D71" s="26" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="26.4">
+      <c r="D71" s="5" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="25">
       <c r="A72" t="s">
         <v>223</v>
       </c>
       <c r="B72" t="s">
         <v>221</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D72" s="26" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="26.4">
+      <c r="D72" s="5" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="25">
       <c r="A73" t="s">
         <v>224</v>
       </c>
@@ -5691,8 +5764,8 @@
       <c r="C73" t="s">
         <v>226</v>
       </c>
-      <c r="D73" s="26" t="s">
-        <v>733</v>
+      <c r="D73" s="5" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -5705,22 +5778,22 @@
       <c r="C74" t="s">
         <v>229</v>
       </c>
-      <c r="D74" s="26" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="26.4">
+      <c r="D74" s="5" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="25">
       <c r="A75" t="s">
         <v>230</v>
       </c>
       <c r="B75" t="s">
         <v>231</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D75" s="26" t="s">
-        <v>735</v>
+      <c r="D75" s="5" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -5733,11 +5806,11 @@
       <c r="C76" t="s">
         <v>235</v>
       </c>
-      <c r="D76" s="26" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="26.4">
+      <c r="D76" s="5" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="25">
       <c r="A77" t="s">
         <v>236</v>
       </c>
@@ -5747,22 +5820,22 @@
       <c r="C77" t="s">
         <v>238</v>
       </c>
-      <c r="D77" s="26" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="26.4">
+      <c r="D77" s="5" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="25">
       <c r="A78" t="s">
         <v>239</v>
       </c>
       <c r="B78" t="s">
         <v>240</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D78" s="26" t="s">
-        <v>738</v>
+      <c r="D78" s="5" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -5775,8 +5848,8 @@
       <c r="C79" t="s">
         <v>243</v>
       </c>
-      <c r="D79" s="26" t="s">
-        <v>739</v>
+      <c r="D79" s="5" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -5789,8 +5862,8 @@
       <c r="C80" t="s">
         <v>247</v>
       </c>
-      <c r="D80" s="26" t="s">
-        <v>740</v>
+      <c r="D80" s="5" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -5803,8 +5876,8 @@
       <c r="C81" t="s">
         <v>250</v>
       </c>
-      <c r="D81" s="26" t="s">
-        <v>741</v>
+      <c r="D81" s="5" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -5817,22 +5890,22 @@
       <c r="C82" t="s">
         <v>253</v>
       </c>
-      <c r="D82" s="26" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="26.4">
+      <c r="D82" s="5" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="25">
       <c r="A83" t="s">
         <v>254</v>
       </c>
       <c r="B83" t="s">
         <v>255</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D83" s="26" t="s">
-        <v>743</v>
+      <c r="D83" s="5" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -5845,8 +5918,8 @@
       <c r="C84" t="s">
         <v>259</v>
       </c>
-      <c r="D84" s="26" t="s">
-        <v>744</v>
+      <c r="D84" s="5" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -5859,8 +5932,8 @@
       <c r="C85" t="s">
         <v>262</v>
       </c>
-      <c r="D85" s="26" t="s">
-        <v>745</v>
+      <c r="D85" s="5" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -5873,11 +5946,11 @@
       <c r="C86" t="s">
         <v>264</v>
       </c>
-      <c r="D86" s="26" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="26.4">
+      <c r="D86" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>265</v>
       </c>
@@ -5887,92 +5960,92 @@
       <c r="C87" t="s">
         <v>270</v>
       </c>
-      <c r="D87" s="26" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="26.4">
+      <c r="D87" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="25">
       <c r="A88" t="s">
         <v>267</v>
       </c>
       <c r="B88" t="s">
         <v>268</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D88" s="26" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="26.4">
+      <c r="D88" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="25">
       <c r="A89" t="s">
         <v>271</v>
       </c>
       <c r="B89" t="s">
         <v>272</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D89" s="26" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="26.4">
+      <c r="D89" s="5" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="25">
       <c r="A90" t="s">
         <v>274</v>
       </c>
       <c r="B90" t="s">
         <v>275</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D90" s="26" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="39.6">
+      <c r="D90" s="5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="37.5">
       <c r="A91" t="s">
         <v>277</v>
       </c>
       <c r="B91" t="s">
         <v>278</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D91" s="30" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="26.4">
+      <c r="D91" s="11" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="25">
       <c r="A92" t="s">
         <v>280</v>
       </c>
       <c r="B92" t="s">
         <v>281</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D92" s="29" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="26.4">
+      <c r="D92" s="8" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="25">
       <c r="A93" t="s">
         <v>283</v>
       </c>
       <c r="B93" t="s">
         <v>284</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D93" s="29" t="s">
-        <v>753</v>
+      <c r="D93" s="8" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -5982,11 +6055,11 @@
       <c r="B94" t="s">
         <v>287</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D94" s="29" t="s">
-        <v>754</v>
+      <c r="D94" s="8" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -5996,11 +6069,11 @@
       <c r="B95" t="s">
         <v>290</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D95" s="29" t="s">
-        <v>755</v>
+      <c r="D95" s="8" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6010,11 +6083,11 @@
       <c r="B96" t="s">
         <v>292</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D96" s="29" t="s">
-        <v>756</v>
+      <c r="D96" s="8" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6024,11 +6097,11 @@
       <c r="B97" t="s">
         <v>295</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D97" s="29" t="s">
-        <v>757</v>
+      <c r="D97" s="8" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6038,53 +6111,53 @@
       <c r="B98" t="s">
         <v>297</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D98" s="29" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="26.4">
+      <c r="D98" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="25">
       <c r="A99" t="s">
         <v>299</v>
       </c>
       <c r="B99" t="s">
         <v>300</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D99" s="29" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="26.4">
+      <c r="D99" s="8" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="25">
       <c r="A100" t="s">
         <v>304</v>
       </c>
       <c r="B100" t="s">
         <v>305</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D100" s="29" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="26.4">
+      <c r="D100" s="8" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="25">
       <c r="A101" t="s">
         <v>307</v>
       </c>
       <c r="B101" t="s">
         <v>308</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D101" s="29" t="s">
-        <v>761</v>
+      <c r="D101" s="8" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -6094,11 +6167,11 @@
       <c r="B102" t="s">
         <v>311</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D102" s="29" t="s">
-        <v>762</v>
+      <c r="D102" s="8" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -6108,39 +6181,39 @@
       <c r="B103" t="s">
         <v>314</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D103" s="29" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="26.4">
+      <c r="D103" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="25">
       <c r="A104" t="s">
         <v>316</v>
       </c>
       <c r="B104" t="s">
         <v>317</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D104" s="32" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="26.4">
+      <c r="D104" s="12" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="25">
       <c r="A105" t="s">
         <v>319</v>
       </c>
       <c r="B105" t="s">
         <v>320</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D105" s="28" t="s">
-        <v>765</v>
+      <c r="D105" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6150,11 +6223,11 @@
       <c r="B106" t="s">
         <v>324</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D106" s="28" t="s">
-        <v>766</v>
+      <c r="D106" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6164,11 +6237,11 @@
       <c r="B107" t="s">
         <v>326</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D107" s="28" t="s">
-        <v>767</v>
+      <c r="D107" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6176,69 +6249,69 @@
         <v>328</v>
       </c>
       <c r="B108" t="s">
-        <v>329</v>
-      </c>
-      <c r="C108" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D108" s="28" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="26.4">
+      <c r="D108" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="25">
       <c r="A109" t="s">
         <v>331</v>
       </c>
       <c r="B109" t="s">
         <v>332</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D109" s="28" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="52.8">
+      <c r="D109" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="37.5">
       <c r="A110" t="s">
         <v>334</v>
       </c>
       <c r="B110" t="s">
         <v>335</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D110" s="31" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="26.4">
+      <c r="D110" s="5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="25">
       <c r="A111" t="s">
         <v>337</v>
       </c>
       <c r="B111" t="s">
         <v>338</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D111" s="31" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="26.4">
+      <c r="D111" s="5" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="25">
       <c r="A112" t="s">
         <v>340</v>
       </c>
       <c r="B112" t="s">
         <v>341</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D112" s="28" t="s">
-        <v>772</v>
+      <c r="D112" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -6248,11 +6321,11 @@
       <c r="B113" t="s">
         <v>344</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D113" s="28" t="s">
-        <v>911</v>
+      <c r="D113" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -6262,11 +6335,11 @@
       <c r="B114" t="s">
         <v>347</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D114" s="28" t="s">
-        <v>774</v>
+      <c r="D114" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6276,11 +6349,11 @@
       <c r="B115" t="s">
         <v>350</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D115" s="28" t="s">
-        <v>775</v>
+      <c r="D115" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6290,25 +6363,25 @@
       <c r="B116" t="s">
         <v>353</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D116" s="28" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="26.4">
+      <c r="D116" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="25">
       <c r="A117" t="s">
         <v>355</v>
       </c>
       <c r="B117" t="s">
         <v>356</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D117" s="28" t="s">
-        <v>777</v>
+      <c r="D117" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6318,25 +6391,25 @@
       <c r="B118" t="s">
         <v>359</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D118" s="31" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="26.4">
+      <c r="D118" s="5" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="25">
       <c r="A119" t="s">
         <v>361</v>
       </c>
       <c r="B119" t="s">
         <v>362</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D119" s="31" t="s">
-        <v>779</v>
+      <c r="D119" s="5" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6346,11 +6419,11 @@
       <c r="B120" t="s">
         <v>368</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D120" s="31" t="s">
-        <v>780</v>
+      <c r="D120" s="5" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6360,11 +6433,11 @@
       <c r="B121" t="s">
         <v>367</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="D121" s="31" t="s">
-        <v>781</v>
+      <c r="D121" s="5" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6374,53 +6447,53 @@
       <c r="B122" t="s">
         <v>371</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D122" s="31" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="26.4">
+      <c r="D122" s="5" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="25">
       <c r="A123" t="s">
         <v>373</v>
       </c>
       <c r="B123" t="s">
         <v>374</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D123" s="31" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="26.4">
+      <c r="D123" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="25">
       <c r="A124" t="s">
         <v>375</v>
       </c>
       <c r="B124" t="s">
         <v>376</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D124" s="31" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="26.4">
+      <c r="D124" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="25">
       <c r="A125" t="s">
         <v>379</v>
       </c>
       <c r="B125" t="s">
         <v>380</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="D125" s="31" t="s">
-        <v>785</v>
+      <c r="D125" s="5" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -6430,11 +6503,11 @@
       <c r="B126" t="s">
         <v>383</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D126" s="31" t="s">
-        <v>786</v>
+      <c r="D126" s="5" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -6444,11 +6517,11 @@
       <c r="B127" t="s">
         <v>386</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D127" s="31" t="s">
-        <v>787</v>
+      <c r="D127" s="5" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -6458,11 +6531,11 @@
       <c r="B128" t="s">
         <v>389</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D128" s="31" t="s">
-        <v>788</v>
+      <c r="D128" s="5" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -6472,81 +6545,81 @@
       <c r="B129" t="s">
         <v>392</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D129" s="31" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="26.4">
+      <c r="D129" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="25">
       <c r="A130" t="s">
         <v>394</v>
       </c>
       <c r="B130" t="s">
         <v>395</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D130" s="31" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="39.6">
+      <c r="D130" s="5" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="37.5">
       <c r="A131" t="s">
         <v>397</v>
       </c>
       <c r="B131" t="s">
         <v>398</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D131" s="31" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="26.4">
+      <c r="D131" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="25">
       <c r="A132" t="s">
         <v>400</v>
       </c>
       <c r="B132" t="s">
         <v>401</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D132" s="31" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="26.4">
+      <c r="D132" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="25">
       <c r="A133" t="s">
         <v>403</v>
       </c>
       <c r="B133" t="s">
         <v>404</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D133" s="31" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="26.4">
+      <c r="D133" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="25">
       <c r="A134" t="s">
         <v>406</v>
       </c>
       <c r="B134" t="s">
         <v>407</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D134" s="31" t="s">
-        <v>794</v>
+      <c r="D134" s="5" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -6556,11 +6629,11 @@
       <c r="B135" t="s">
         <v>410</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D135" s="31" t="s">
-        <v>795</v>
+      <c r="D135" s="5" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -6570,11 +6643,11 @@
       <c r="B136" t="s">
         <v>413</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D136" s="31" t="s">
-        <v>796</v>
+      <c r="D136" s="5" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -6584,11 +6657,11 @@
       <c r="B137" t="s">
         <v>416</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D137" s="31" t="s">
-        <v>797</v>
+      <c r="D137" s="5" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -6598,11 +6671,11 @@
       <c r="B138" t="s">
         <v>419</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D138" s="31" t="s">
-        <v>798</v>
+      <c r="D138" s="5" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -6612,11 +6685,11 @@
       <c r="B139" t="s">
         <v>422</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D139" s="31" t="s">
-        <v>799</v>
+      <c r="D139" s="5" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -6626,11 +6699,11 @@
       <c r="B140" t="s">
         <v>63</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D140" s="31" t="s">
-        <v>800</v>
+      <c r="D140" s="5" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -6640,11 +6713,11 @@
       <c r="B141" t="s">
         <v>426</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="D141" s="31" t="s">
-        <v>801</v>
+      <c r="D141" s="5" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -6654,11 +6727,11 @@
       <c r="B142" t="s">
         <v>429</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D142" s="31" t="s">
-        <v>802</v>
+      <c r="D142" s="5" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -6668,25 +6741,25 @@
       <c r="B143" t="s">
         <v>432</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="D143" s="31" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="39.6">
+      <c r="D143" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="37.5">
       <c r="A144" t="s">
         <v>434</v>
       </c>
       <c r="B144" t="s">
         <v>435</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D144" s="31" t="s">
-        <v>804</v>
+      <c r="D144" s="5" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -6696,25 +6769,25 @@
       <c r="B145" t="s">
         <v>438</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D145" s="31" t="s">
-        <v>805</v>
+      <c r="D145" s="5" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
+        <v>645</v>
+      </c>
+      <c r="B146" t="s">
         <v>646</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="C146" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="D146" s="31" t="s">
-        <v>806</v>
+      <c r="D146" s="5" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -6724,11 +6797,11 @@
       <c r="B147" t="s">
         <v>441</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="D147" s="31" t="s">
-        <v>807</v>
+      <c r="D147" s="5" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -6738,11 +6811,11 @@
       <c r="B148" t="s">
         <v>444</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D148" s="31" t="s">
-        <v>808</v>
+      <c r="D148" s="5" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -6752,11 +6825,11 @@
       <c r="B149" t="s">
         <v>447</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D149" s="31" t="s">
-        <v>809</v>
+      <c r="D149" s="5" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -6766,25 +6839,25 @@
       <c r="B150" t="s">
         <v>450</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D150" s="31" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="26.4">
+      <c r="D150" s="5" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="25">
       <c r="A151" t="s">
         <v>452</v>
       </c>
       <c r="B151" t="s">
         <v>453</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="D151" s="31" t="s">
-        <v>811</v>
+      <c r="D151" s="5" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -6794,11 +6867,11 @@
       <c r="B152" t="s">
         <v>456</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="D152" s="31" t="s">
-        <v>812</v>
+      <c r="D152" s="5" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -6808,53 +6881,53 @@
       <c r="B153" t="s">
         <v>459</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D153" s="31" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="26.4">
+      <c r="D153" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="25">
       <c r="A154" t="s">
         <v>461</v>
       </c>
       <c r="B154" t="s">
         <v>462</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D154" s="31" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="26.4">
+      <c r="D154" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="25">
       <c r="A155" t="s">
         <v>464</v>
       </c>
       <c r="B155" t="s">
         <v>465</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D155" s="31" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="26.4">
+      <c r="D155" s="5" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="25">
       <c r="A156" t="s">
         <v>467</v>
       </c>
       <c r="B156" t="s">
         <v>468</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D156" s="31" t="s">
-        <v>816</v>
+      <c r="D156" s="5" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -6864,39 +6937,39 @@
       <c r="B157" t="s">
         <v>471</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D157" s="31" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="26.4">
+      <c r="D157" s="5" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="25">
       <c r="A158" t="s">
         <v>473</v>
       </c>
       <c r="B158" t="s">
         <v>474</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="D158" s="31" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="26.4">
+      <c r="D158" s="5" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="25">
       <c r="A159" t="s">
         <v>476</v>
       </c>
       <c r="B159" t="s">
         <v>477</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="D159" s="31" t="s">
-        <v>819</v>
+      <c r="D159" s="5" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -6906,53 +6979,53 @@
       <c r="B160" t="s">
         <v>480</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D160" s="31" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="26.4">
+      <c r="D160" s="5" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="25">
       <c r="A161" t="s">
         <v>482</v>
       </c>
       <c r="B161" t="s">
         <v>483</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D161" s="31" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="26.4">
+      <c r="D161" s="5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="25">
       <c r="A162" t="s">
         <v>485</v>
       </c>
       <c r="B162" t="s">
         <v>486</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="D162" s="31" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="26.4">
+      <c r="D162" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>489</v>
       </c>
       <c r="B163" t="s">
         <v>488</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="D163" s="31" t="s">
-        <v>823</v>
+      <c r="D163" s="5" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -6962,11 +7035,11 @@
       <c r="B164" t="s">
         <v>492</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D164" s="31" t="s">
-        <v>824</v>
+      <c r="D164" s="5" t="s">
+        <v>823</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -6976,25 +7049,25 @@
       <c r="B165" t="s">
         <v>495</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D165" s="31" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="26.4">
+      <c r="D165" s="5" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="25">
       <c r="A166" t="s">
         <v>497</v>
       </c>
       <c r="B166" t="s">
         <v>498</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D166" s="31" t="s">
-        <v>826</v>
+      <c r="D166" s="5" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -7004,25 +7077,25 @@
       <c r="B167" t="s">
         <v>501</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D167" s="31" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="26.4">
+      <c r="D167" s="5" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="25">
       <c r="A168" t="s">
         <v>503</v>
       </c>
       <c r="B168" t="s">
         <v>504</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D168" s="31" t="s">
-        <v>828</v>
+      <c r="D168" s="5" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -7032,123 +7105,123 @@
       <c r="B169" t="s">
         <v>507</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D169" s="31" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="26.4">
+      <c r="D169" s="5" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="25">
       <c r="A170" t="s">
         <v>509</v>
       </c>
       <c r="B170" t="s">
         <v>510</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="D170" s="31" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="26.4">
+      <c r="D170" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="25">
       <c r="A171" t="s">
         <v>512</v>
       </c>
       <c r="B171" t="s">
         <v>513</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="D171" s="31" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="26.4">
+      <c r="D171" s="5" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="25">
       <c r="A172" t="s">
         <v>515</v>
       </c>
       <c r="B172" t="s">
         <v>516</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="D172" s="31" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="26.4">
+      <c r="D172" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="25">
       <c r="A173" t="s">
         <v>518</v>
       </c>
       <c r="B173" t="s">
         <v>519</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D173" s="31" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="26.4">
+      <c r="D173" s="5" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="25">
       <c r="A174" t="s">
         <v>521</v>
       </c>
       <c r="B174" t="s">
         <v>522</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="D174" s="31" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="26.4">
+      <c r="D174" s="5" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="25">
       <c r="A175" t="s">
         <v>525</v>
       </c>
       <c r="B175" t="s">
         <v>524</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D175" s="31" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="39.6">
+      <c r="D175" s="5" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="37.5">
       <c r="A176" t="s">
         <v>528</v>
       </c>
       <c r="B176" t="s">
         <v>527</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="D176" s="31" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="26.4">
+      <c r="D176" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="25">
       <c r="A177" t="s">
         <v>531</v>
       </c>
       <c r="B177" t="s">
         <v>530</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D177" s="31" t="s">
-        <v>837</v>
+      <c r="D177" s="5" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -7158,11 +7231,11 @@
       <c r="B178" t="s">
         <v>533</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="D178" s="31" t="s">
-        <v>838</v>
+      <c r="D178" s="5" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -7172,63 +7245,63 @@
       <c r="B179" t="s">
         <v>537</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="D179" s="31" t="s">
-        <v>839</v>
+      <c r="D179" s="5" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="D182" s="31"/>
+      <c r="D182" s="5"/>
     </row>
     <row r="183" spans="1:4">
-      <c r="D183" s="31"/>
+      <c r="D183" s="5"/>
     </row>
     <row r="184" spans="1:4">
-      <c r="D184" s="31"/>
+      <c r="D184" s="5"/>
     </row>
     <row r="185" spans="1:4">
-      <c r="D185" s="31"/>
+      <c r="D185" s="5"/>
     </row>
     <row r="186" spans="1:4">
-      <c r="D186" s="31"/>
+      <c r="D186" s="5"/>
     </row>
     <row r="187" spans="1:4">
-      <c r="D187" s="31"/>
+      <c r="D187" s="5"/>
     </row>
     <row r="188" spans="1:4">
-      <c r="D188" s="31"/>
+      <c r="D188" s="5"/>
     </row>
     <row r="189" spans="1:4">
-      <c r="D189" s="31"/>
+      <c r="D189" s="5"/>
     </row>
     <row r="190" spans="1:4">
-      <c r="D190" s="31"/>
+      <c r="D190" s="5"/>
     </row>
     <row r="191" spans="1:4">
-      <c r="D191" s="31"/>
+      <c r="D191" s="5"/>
     </row>
     <row r="192" spans="1:4">
-      <c r="D192" s="31"/>
+      <c r="D192" s="5"/>
     </row>
     <row r="193" spans="4:4">
-      <c r="D193" s="31"/>
+      <c r="D193" s="5"/>
     </row>
     <row r="194" spans="4:4">
-      <c r="D194" s="31"/>
+      <c r="D194" s="5"/>
     </row>
     <row r="195" spans="4:4">
-      <c r="D195" s="31"/>
+      <c r="D195" s="5"/>
     </row>
     <row r="196" spans="4:4">
-      <c r="D196" s="31"/>
+      <c r="D196" s="5"/>
     </row>
     <row r="197" spans="4:4">
-      <c r="D197" s="31"/>
+      <c r="D197" s="5"/>
     </row>
     <row r="198" spans="4:4">
-      <c r="D198" s="31"/>
+      <c r="D198" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -7237,14 +7310,14 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D241"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D260"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="52.77734375" customWidth="1"/>
-    <col min="2" max="2" width="50.21875" customWidth="1"/>
-    <col min="3" max="3" width="61.77734375" customWidth="1"/>
-    <col min="4" max="4" width="37.21875" customWidth="1"/>
+    <col min="1" max="1" width="52.81640625" customWidth="1"/>
+    <col min="2" max="2" width="50.1796875" customWidth="1"/>
+    <col min="3" max="3" width="61.81640625" customWidth="1"/>
+    <col min="4" max="4" width="37.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -7257,22 +7330,22 @@
       <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="26.4">
+      <c r="D1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25">
       <c r="A2" t="s">
         <v>199</v>
       </c>
       <c r="B2" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>722</v>
+      <c r="D2" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7280,13 +7353,13 @@
         <v>201</v>
       </c>
       <c r="B3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C3" t="s">
         <v>649</v>
       </c>
-      <c r="C3" t="s">
-        <v>650</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>723</v>
+      <c r="D3" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7299,8 +7372,8 @@
       <c r="C4" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>724</v>
+      <c r="D4" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7313,8 +7386,8 @@
       <c r="C5" t="s">
         <v>602</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>725</v>
+      <c r="D5" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7324,11 +7397,11 @@
       <c r="B6" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>726</v>
+      <c r="D6" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7341,8 +7414,8 @@
       <c r="C7" t="s">
         <v>210</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>727</v>
+      <c r="D7" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7355,8 +7428,8 @@
       <c r="C8" t="s">
         <v>605</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>728</v>
+      <c r="D8" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7369,8 +7442,8 @@
       <c r="C9" t="s">
         <v>215</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>729</v>
+      <c r="D9" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7380,11 +7453,11 @@
       <c r="B10" t="s">
         <v>217</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D10" s="19" t="s">
-        <v>730</v>
+      <c r="D10" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7394,25 +7467,25 @@
       <c r="B11" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="26.4">
+      <c r="D11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="25">
       <c r="A12" t="s">
         <v>223</v>
       </c>
       <c r="B12" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>732</v>
+      <c r="D12" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7425,8 +7498,8 @@
       <c r="C13" t="s">
         <v>539</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>733</v>
+      <c r="D13" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7439,22 +7512,22 @@
       <c r="C14" t="s">
         <v>229</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="26.4">
+      <c r="D14" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="25">
       <c r="A15" t="s">
         <v>230</v>
       </c>
       <c r="B15" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>735</v>
+      <c r="D15" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7467,8 +7540,8 @@
       <c r="C16" t="s">
         <v>235</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>736</v>
+      <c r="D16" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -7481,22 +7554,22 @@
       <c r="C17" t="s">
         <v>540</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="26.4">
+      <c r="D17" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="25">
       <c r="A18" t="s">
         <v>239</v>
       </c>
       <c r="B18" t="s">
         <v>240</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>738</v>
+      <c r="D18" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -7509,8 +7582,8 @@
       <c r="C19" t="s">
         <v>243</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>739</v>
+      <c r="D19" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -7523,8 +7596,8 @@
       <c r="C20" t="s">
         <v>247</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>740</v>
+      <c r="D20" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -7537,8 +7610,8 @@
       <c r="C21" t="s">
         <v>250</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>741</v>
+      <c r="D21" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -7551,22 +7624,22 @@
       <c r="C22" t="s">
         <v>253</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="26.4">
+      <c r="D22" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="25">
       <c r="A23" t="s">
         <v>254</v>
       </c>
       <c r="B23" t="s">
         <v>255</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>743</v>
+      <c r="D23" s="8" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -7579,8 +7652,8 @@
       <c r="C24" t="s">
         <v>259</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>744</v>
+      <c r="D24" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -7593,8 +7666,8 @@
       <c r="C25" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="19" t="s">
-        <v>745</v>
+      <c r="D25" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -7607,8 +7680,8 @@
       <c r="C26" t="s">
         <v>264</v>
       </c>
-      <c r="D26" s="19" t="s">
-        <v>746</v>
+      <c r="D26" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -7621,92 +7694,92 @@
       <c r="C27" t="s">
         <v>270</v>
       </c>
-      <c r="D27" s="19" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="26.4">
+      <c r="D27" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="25">
       <c r="A28" t="s">
         <v>267</v>
       </c>
       <c r="B28" t="s">
         <v>268</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="26.4">
+      <c r="D28" s="8" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="25">
       <c r="A29" t="s">
         <v>271</v>
       </c>
       <c r="B29" t="s">
         <v>272</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D29" s="19" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="26.4">
+      <c r="D29" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="25">
       <c r="A30" t="s">
         <v>274</v>
       </c>
       <c r="B30" t="s">
         <v>275</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D30" s="20" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="26.4">
+      <c r="D30" s="8" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="25">
       <c r="A31" t="s">
         <v>277</v>
       </c>
       <c r="B31" t="s">
         <v>278</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="26.4">
+      <c r="D31" s="11" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="25">
       <c r="A32" t="s">
         <v>280</v>
       </c>
       <c r="B32" t="s">
         <v>281</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D32" s="20" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="26.4">
+      <c r="D32" s="8" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="25">
       <c r="A33" t="s">
         <v>283</v>
       </c>
       <c r="B33" t="s">
         <v>284</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>753</v>
+      <c r="D33" s="8" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -7716,11 +7789,11 @@
       <c r="B34" t="s">
         <v>287</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>754</v>
+      <c r="D34" s="8" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -7730,11 +7803,11 @@
       <c r="B35" t="s">
         <v>290</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>755</v>
+      <c r="D35" s="8" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -7744,11 +7817,11 @@
       <c r="B36" t="s">
         <v>292</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>756</v>
+      <c r="D36" s="8" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -7758,11 +7831,11 @@
       <c r="B37" t="s">
         <v>295</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>757</v>
+      <c r="D37" s="8" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -7772,53 +7845,53 @@
       <c r="B38" t="s">
         <v>297</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="26.4">
+      <c r="D38" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="25">
       <c r="A39" t="s">
         <v>299</v>
       </c>
       <c r="B39" t="s">
         <v>300</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="26.4">
+      <c r="D39" s="8" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="25">
       <c r="A40" t="s">
         <v>304</v>
       </c>
       <c r="B40" t="s">
         <v>305</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="26.4">
+      <c r="D40" s="8" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="25">
       <c r="A41" t="s">
         <v>307</v>
       </c>
       <c r="B41" t="s">
         <v>308</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>761</v>
+      <c r="D41" s="8" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -7828,11 +7901,11 @@
       <c r="B42" t="s">
         <v>311</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D42" s="20" t="s">
-        <v>762</v>
+      <c r="D42" s="8" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -7842,11 +7915,11 @@
       <c r="B43" t="s">
         <v>314</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>763</v>
+      <c r="D43" s="8" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -7856,25 +7929,25 @@
       <c r="B44" t="s">
         <v>317</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="D44" s="23" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="26.4">
+      <c r="D44" s="12" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="25">
       <c r="A45" t="s">
         <v>319</v>
       </c>
       <c r="B45" t="s">
         <v>320</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D45" s="22" t="s">
-        <v>765</v>
+      <c r="D45" s="5" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -7884,11 +7957,11 @@
       <c r="B46" t="s">
         <v>324</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D46" s="20" t="s">
-        <v>766</v>
+      <c r="D46" s="8" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -7898,11 +7971,11 @@
       <c r="B47" t="s">
         <v>326</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D47" s="20" t="s">
-        <v>767</v>
+      <c r="D47" s="8" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -7912,67 +7985,67 @@
       <c r="B48" t="s">
         <v>329</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D48" s="22" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="26.4">
+      <c r="D48" s="5" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="25">
       <c r="A49" t="s">
         <v>331</v>
       </c>
       <c r="B49" t="s">
         <v>332</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="26.4">
+      <c r="D49" s="8" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="25">
       <c r="A50" t="s">
         <v>334</v>
       </c>
       <c r="B50" t="s">
         <v>335</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D50" s="22" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="26.4">
+      <c r="D50" s="5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="25">
       <c r="A51" t="s">
         <v>337</v>
       </c>
       <c r="B51" t="s">
         <v>338</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D51" s="22" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="26.4">
+      <c r="D51" s="5" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="25">
       <c r="A52" t="s">
         <v>340</v>
       </c>
       <c r="B52" t="s">
         <v>341</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>772</v>
+      <c r="D52" s="8" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -7982,11 +8055,11 @@
       <c r="B53" t="s">
         <v>344</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="D53" s="22" t="s">
-        <v>773</v>
+      <c r="D53" s="5" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -7996,11 +8069,11 @@
       <c r="B54" t="s">
         <v>347</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D54" s="22" t="s">
-        <v>774</v>
+      <c r="D54" s="5" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -8010,11 +8083,11 @@
       <c r="B55" t="s">
         <v>350</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D55" s="22" t="s">
-        <v>775</v>
+      <c r="D55" s="5" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -8024,25 +8097,25 @@
       <c r="B56" t="s">
         <v>353</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D56" s="22" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="26.4">
+      <c r="D56" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="25">
       <c r="A57" t="s">
         <v>355</v>
       </c>
       <c r="B57" t="s">
         <v>356</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D57" s="22" t="s">
-        <v>777</v>
+      <c r="D57" s="5" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -8052,25 +8125,25 @@
       <c r="B58" t="s">
         <v>359</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D58" s="22" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="26.4">
+      <c r="D58" s="5" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="25">
       <c r="A59" t="s">
         <v>361</v>
       </c>
       <c r="B59" t="s">
         <v>362</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D59" s="22" t="s">
-        <v>779</v>
+      <c r="D59" s="5" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -8080,11 +8153,11 @@
       <c r="B60" t="s">
         <v>368</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D60" s="22" t="s">
-        <v>780</v>
+      <c r="D60" s="5" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -8094,11 +8167,11 @@
       <c r="B61" t="s">
         <v>367</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="D61" s="22" t="s">
-        <v>781</v>
+      <c r="D61" s="5" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -8108,25 +8181,25 @@
       <c r="B62" t="s">
         <v>371</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D62" s="22" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="26.4">
+      <c r="D62" s="5" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="25">
       <c r="A63" t="s">
         <v>373</v>
       </c>
       <c r="B63" t="s">
         <v>374</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D63" s="22" t="s">
-        <v>783</v>
+      <c r="D63" s="5" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -8136,11 +8209,11 @@
       <c r="B64" t="s">
         <v>376</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D64" s="22" t="s">
-        <v>784</v>
+      <c r="D64" s="5" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -8150,11 +8223,11 @@
       <c r="B65" t="s">
         <v>380</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="D65" s="22" t="s">
-        <v>785</v>
+      <c r="D65" s="5" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -8164,11 +8237,11 @@
       <c r="B66" t="s">
         <v>593</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="D66" s="22" t="s">
-        <v>786</v>
+      <c r="D66" s="5" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -8178,11 +8251,11 @@
       <c r="B67" t="s">
         <v>595</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="D67" s="22" t="s">
-        <v>787</v>
+      <c r="D67" s="5" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -8192,11 +8265,11 @@
       <c r="B68" t="s">
         <v>389</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D68" s="22" t="s">
-        <v>788</v>
+      <c r="D68" s="5" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -8206,53 +8279,53 @@
       <c r="B69" t="s">
         <v>392</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D69" s="22" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="26.4">
+      <c r="D69" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="25">
       <c r="A70" t="s">
         <v>394</v>
       </c>
       <c r="B70" t="s">
         <v>395</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D70" s="22" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="26.4">
+      <c r="D70" s="5" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="25">
       <c r="A71" t="s">
         <v>397</v>
       </c>
       <c r="B71" t="s">
         <v>398</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D71" s="22" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="26.4">
+      <c r="D71" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="25">
       <c r="A72" t="s">
         <v>400</v>
       </c>
       <c r="B72" t="s">
         <v>401</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D72" s="22" t="s">
-        <v>792</v>
+      <c r="D72" s="5" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -8262,25 +8335,25 @@
       <c r="B73" t="s">
         <v>404</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D73" s="22" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="26.4">
+      <c r="D73" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="25">
       <c r="A74" t="s">
         <v>406</v>
       </c>
       <c r="B74" t="s">
         <v>407</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D74" s="22" t="s">
-        <v>794</v>
+      <c r="D74" s="5" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -8290,11 +8363,11 @@
       <c r="B75" t="s">
         <v>410</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D75" s="22" t="s">
-        <v>795</v>
+      <c r="D75" s="5" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -8304,11 +8377,11 @@
       <c r="B76" t="s">
         <v>413</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D76" s="22" t="s">
-        <v>796</v>
+      <c r="D76" s="5" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -8318,11 +8391,11 @@
       <c r="B77" t="s">
         <v>416</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="D77" s="22" t="s">
-        <v>797</v>
+      <c r="D77" s="5" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -8332,11 +8405,11 @@
       <c r="B78" t="s">
         <v>419</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D78" s="22" t="s">
-        <v>798</v>
+      <c r="D78" s="5" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -8346,25 +8419,25 @@
       <c r="B79" t="s">
         <v>422</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D79" s="22" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="26.4">
+      <c r="D79" s="5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="25">
       <c r="A80" t="s">
         <v>424</v>
       </c>
       <c r="B80" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="D80" s="22" t="s">
-        <v>800</v>
+      <c r="D80" s="5" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -8374,11 +8447,11 @@
       <c r="B81" t="s">
         <v>426</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="D81" s="22" t="s">
-        <v>801</v>
+      <c r="D81" s="5" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -8388,11 +8461,11 @@
       <c r="B82" t="s">
         <v>429</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D82" s="22" t="s">
-        <v>802</v>
+      <c r="D82" s="5" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -8402,25 +8475,25 @@
       <c r="B83" t="s">
         <v>432</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="D83" s="22" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="26.4">
+      <c r="D83" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="25">
       <c r="A84" t="s">
         <v>434</v>
       </c>
       <c r="B84" t="s">
         <v>435</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D84" s="22" t="s">
-        <v>804</v>
+      <c r="D84" s="5" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -8430,25 +8503,25 @@
       <c r="B85" t="s">
         <v>438</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D85" s="22" t="s">
-        <v>805</v>
+      <c r="D85" s="5" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
+        <v>645</v>
+      </c>
+      <c r="B86" t="s">
         <v>646</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="D86" s="22" t="s">
-        <v>806</v>
+      <c r="D86" s="5" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -8458,11 +8531,11 @@
       <c r="B87" t="s">
         <v>441</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="D87" s="22" t="s">
-        <v>807</v>
+      <c r="D87" s="5" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -8472,11 +8545,11 @@
       <c r="B88" t="s">
         <v>444</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D88" s="22" t="s">
-        <v>808</v>
+      <c r="D88" s="5" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -8486,11 +8559,11 @@
       <c r="B89" t="s">
         <v>447</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D89" s="22" t="s">
-        <v>809</v>
+      <c r="D89" s="5" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -8500,11 +8573,11 @@
       <c r="B90" t="s">
         <v>450</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D90" s="22" t="s">
-        <v>810</v>
+      <c r="D90" s="5" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -8514,11 +8587,11 @@
       <c r="B91" t="s">
         <v>453</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="D91" s="22" t="s">
-        <v>811</v>
+      <c r="D91" s="5" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -8528,11 +8601,11 @@
       <c r="B92" t="s">
         <v>456</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="D92" s="22" t="s">
-        <v>812</v>
+      <c r="D92" s="5" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -8542,53 +8615,53 @@
       <c r="B93" t="s">
         <v>459</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D93" s="22" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="26.4">
+      <c r="D93" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="25">
       <c r="A94" t="s">
         <v>461</v>
       </c>
       <c r="B94" t="s">
         <v>462</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D94" s="22" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="26.4">
+      <c r="D94" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="25">
       <c r="A95" t="s">
         <v>464</v>
       </c>
       <c r="B95" t="s">
         <v>465</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D95" s="22" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="26.4">
+      <c r="D95" s="5" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="25">
       <c r="A96" t="s">
         <v>467</v>
       </c>
       <c r="B96" t="s">
         <v>468</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D96" s="22" t="s">
-        <v>816</v>
+      <c r="D96" s="5" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -8598,11 +8671,11 @@
       <c r="B97" t="s">
         <v>471</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D97" s="22" t="s">
-        <v>817</v>
+      <c r="D97" s="5" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -8612,11 +8685,11 @@
       <c r="B98" t="s">
         <v>474</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="D98" s="22" t="s">
-        <v>818</v>
+      <c r="D98" s="5" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -8626,11 +8699,11 @@
       <c r="B99" t="s">
         <v>477</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="D99" s="22" t="s">
-        <v>819</v>
+      <c r="D99" s="5" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -8640,25 +8713,25 @@
       <c r="B100" t="s">
         <v>480</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D100" s="22" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="26.4">
+      <c r="D100" s="5" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="25">
       <c r="A101" t="s">
         <v>482</v>
       </c>
       <c r="B101" t="s">
         <v>483</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D101" s="22" t="s">
-        <v>821</v>
+      <c r="D101" s="5" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -8668,11 +8741,11 @@
       <c r="B102" t="s">
         <v>486</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="D102" s="22" t="s">
-        <v>822</v>
+      <c r="D102" s="5" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -8682,11 +8755,11 @@
       <c r="B103" t="s">
         <v>488</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="D103" s="22" t="s">
-        <v>823</v>
+      <c r="D103" s="5" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -8696,11 +8769,11 @@
       <c r="B104" t="s">
         <v>492</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D104" s="22" t="s">
-        <v>824</v>
+      <c r="D104" s="5" t="s">
+        <v>823</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -8710,25 +8783,25 @@
       <c r="B105" t="s">
         <v>495</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D105" s="22" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="26.4">
+      <c r="D105" s="5" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="25">
       <c r="A106" t="s">
         <v>497</v>
       </c>
       <c r="B106" t="s">
         <v>498</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D106" s="22" t="s">
-        <v>826</v>
+      <c r="D106" s="5" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -8738,25 +8811,25 @@
       <c r="B107" t="s">
         <v>501</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="D107" s="22" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="26.4">
+      <c r="D107" s="5" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="25">
       <c r="A108" t="s">
         <v>503</v>
       </c>
       <c r="B108" t="s">
         <v>504</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D108" s="22" t="s">
-        <v>828</v>
+      <c r="D108" s="5" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -8766,67 +8839,67 @@
       <c r="B109" t="s">
         <v>507</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D109" s="22" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="26.4">
+      <c r="D109" s="5" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="25">
       <c r="A110" t="s">
         <v>509</v>
       </c>
       <c r="B110" t="s">
         <v>510</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="D110" s="22" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="26.4">
+      <c r="D110" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="25">
       <c r="A111" t="s">
         <v>512</v>
       </c>
       <c r="B111" t="s">
         <v>513</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="D111" s="22" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="26.4">
+      <c r="D111" s="5" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="25">
       <c r="A112" t="s">
         <v>515</v>
       </c>
       <c r="B112" t="s">
         <v>516</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="D112" s="22" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="26.4">
+      <c r="D112" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="25">
       <c r="A113" t="s">
         <v>518</v>
       </c>
       <c r="B113" t="s">
         <v>519</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D113" s="22" t="s">
-        <v>833</v>
+      <c r="D113" s="5" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -8836,53 +8909,53 @@
       <c r="B114" t="s">
         <v>522</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="D114" s="22" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="26.4">
+      <c r="D114" s="5" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="25">
       <c r="A115" t="s">
         <v>525</v>
       </c>
       <c r="B115" t="s">
         <v>524</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D115" s="22" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="26.4">
+      <c r="D115" s="5" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="25">
       <c r="A116" t="s">
         <v>528</v>
       </c>
       <c r="B116" t="s">
         <v>527</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="D116" s="22" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="26.4">
+      <c r="D116" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="25">
       <c r="A117" t="s">
         <v>531</v>
       </c>
       <c r="B117" t="s">
         <v>530</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D117" s="22" t="s">
-        <v>837</v>
+      <c r="D117" s="5" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -8892,11 +8965,11 @@
       <c r="B118" t="s">
         <v>533</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="D118" s="22" t="s">
-        <v>838</v>
+      <c r="D118" s="5" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -8906,11 +8979,11 @@
       <c r="B119" t="s">
         <v>537</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="D119" s="22" t="s">
-        <v>839</v>
+      <c r="D119" s="5" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -8920,11 +8993,11 @@
       <c r="B120" t="s">
         <v>548</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="D120" s="22" t="s">
-        <v>840</v>
+      <c r="D120" s="5" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -8934,11 +9007,11 @@
       <c r="B121" t="s">
         <v>550</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="D121" s="22" t="s">
-        <v>841</v>
+      <c r="D121" s="5" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -8948,11 +9021,11 @@
       <c r="B122" t="s">
         <v>554</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D122" s="22" t="s">
-        <v>920</v>
+      <c r="D122" s="5" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -8962,25 +9035,25 @@
       <c r="B123" t="s">
         <v>556</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="D123" s="22" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="26.4">
+      <c r="D123" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="25">
       <c r="A124" t="s">
         <v>557</v>
       </c>
       <c r="B124" t="s">
         <v>558</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="D124" s="22" t="s">
-        <v>844</v>
+      <c r="D124" s="5" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -8990,11 +9063,11 @@
       <c r="B125" t="s">
         <v>561</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D125" s="22" t="s">
-        <v>845</v>
+      <c r="D125" s="5" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -9004,11 +9077,11 @@
       <c r="B126" t="s">
         <v>564</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="D126" s="22" t="s">
-        <v>846</v>
+      <c r="D126" s="5" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -9018,11 +9091,11 @@
       <c r="B127" t="s">
         <v>567</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="D127" s="22" t="s">
-        <v>847</v>
+      <c r="D127" s="5" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -9032,11 +9105,11 @@
       <c r="B128" t="s">
         <v>569</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="D128" s="22" t="s">
-        <v>808</v>
+      <c r="D128" s="5" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -9046,11 +9119,11 @@
       <c r="B129" t="s">
         <v>572</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="D129" s="22" t="s">
-        <v>805</v>
+      <c r="D129" s="5" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -9060,39 +9133,39 @@
       <c r="B130" t="s">
         <v>575</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D130" s="22" t="s">
+      <c r="D130" s="5" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="26.4">
+    <row r="131" spans="1:4" ht="25">
       <c r="A131" t="s">
         <v>577</v>
       </c>
       <c r="B131" t="s">
         <v>578</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="D131" s="22" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="26.4">
+      <c r="D131" s="5" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="25">
       <c r="A132" t="s">
         <v>582</v>
       </c>
       <c r="B132" t="s">
         <v>580</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D132" s="22" t="s">
-        <v>849</v>
+      <c r="D132" s="5" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -9102,11 +9175,11 @@
       <c r="B133" t="s">
         <v>584</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="D133" s="22" t="s">
-        <v>850</v>
+      <c r="D133" s="5" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -9116,11 +9189,11 @@
       <c r="B134" t="s">
         <v>587</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="D134" s="22" t="s">
-        <v>851</v>
+      <c r="D134" s="5" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -9130,11 +9203,11 @@
       <c r="B135" t="s">
         <v>598</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="D135" s="22" t="s">
-        <v>852</v>
+      <c r="D135" s="5" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -9144,11 +9217,11 @@
       <c r="B136" t="s">
         <v>607</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="D136" s="22" t="s">
-        <v>853</v>
+      <c r="D136" s="5" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -9158,1164 +9231,1317 @@
       <c r="B137" t="s">
         <v>610</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="D137" s="22" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="26.4">
+      <c r="D137" s="5" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="25">
       <c r="A138" t="s">
         <v>613</v>
       </c>
       <c r="B138" t="s">
         <v>614</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="D138" s="22" t="s">
-        <v>855</v>
+      <c r="D138" s="5" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
+        <v>650</v>
+      </c>
+      <c r="B139" t="s">
         <v>651</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>652</v>
-      </c>
-      <c r="C139" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
+        <v>653</v>
+      </c>
+      <c r="B140" t="s">
         <v>654</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>655</v>
-      </c>
-      <c r="C140" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
+        <v>656</v>
+      </c>
+      <c r="B141" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="C141" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="C141" s="11" t="s">
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="8" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="12" t="s">
+      <c r="B142" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="C142" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="C142" s="11" t="s">
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="8" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="12" t="s">
+      <c r="B143" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="C143" s="5" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="C143" s="11" t="s">
+      <c r="B144" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="C144" s="5" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="B144" s="12" t="s">
+    <row r="145" spans="1:3">
+      <c r="A145" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="C144" s="11" t="s">
+      <c r="B145" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="C145" s="5" t="s">
         <v>670</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>668</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B146" t="s">
+        <v>675</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
+        <v>672</v>
+      </c>
+      <c r="B147" t="s">
         <v>673</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>674</v>
       </c>
-      <c r="C147" t="s">
-        <v>675</v>
-      </c>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="12" t="s">
+      <c r="A148" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="B149" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="B148" s="12" t="s">
-        <v>678</v>
-      </c>
-      <c r="C148" s="11" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" s="12" t="s">
+      <c r="C149" s="5" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="B149" s="12" t="s">
-        <v>681</v>
-      </c>
-      <c r="C149" s="11" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" s="12" t="s">
+      <c r="B150" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="B150" s="12" t="s">
+      <c r="C150" s="5" t="s">
         <v>685</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
+        <v>691</v>
+      </c>
+      <c r="B151" t="s">
         <v>692</v>
       </c>
-      <c r="B151" t="s">
-        <v>693</v>
-      </c>
       <c r="C151" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
+        <v>693</v>
+      </c>
+      <c r="B152" t="s">
         <v>694</v>
       </c>
-      <c r="B152" t="s">
-        <v>695</v>
-      </c>
       <c r="C152" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
+        <v>695</v>
+      </c>
+      <c r="B153" t="s">
         <v>696</v>
       </c>
-      <c r="B153" t="s">
-        <v>697</v>
-      </c>
       <c r="C153" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
+        <v>697</v>
+      </c>
+      <c r="B154" t="s">
         <v>698</v>
       </c>
-      <c r="B154" t="s">
-        <v>699</v>
-      </c>
       <c r="C154" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
+        <v>699</v>
+      </c>
+      <c r="B155" t="s">
         <v>700</v>
       </c>
-      <c r="B155" t="s">
-        <v>701</v>
-      </c>
       <c r="C155" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
+        <v>701</v>
+      </c>
+      <c r="B156" t="s">
         <v>702</v>
       </c>
-      <c r="B156" t="s">
-        <v>703</v>
-      </c>
       <c r="C156" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
+        <v>709</v>
+      </c>
+      <c r="B157" t="s">
         <v>710</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>711</v>
-      </c>
-      <c r="C157" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
+        <v>712</v>
+      </c>
+      <c r="B158" t="s">
+        <v>712</v>
+      </c>
+      <c r="C158" t="s">
         <v>713</v>
-      </c>
-      <c r="B158" t="s">
-        <v>713</v>
-      </c>
-      <c r="C158" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B159" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C159" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B160" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C160" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
+        <v>717</v>
+      </c>
+      <c r="B161" t="s">
         <v>718</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>720</v>
-      </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="38" t="s">
+      <c r="A162" t="s">
+        <v>920</v>
+      </c>
+      <c r="B162" t="s">
+        <v>934</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
         <v>921</v>
       </c>
-      <c r="B162" s="38" t="s">
+      <c r="B163" t="s">
         <v>935</v>
       </c>
-      <c r="C162" s="40" t="s">
+      <c r="C163" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
-      <c r="A163" s="38" t="s">
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
         <v>922</v>
       </c>
-      <c r="B163" s="38" t="s">
+      <c r="B164" t="s">
         <v>936</v>
       </c>
-      <c r="C163" s="38" t="s">
+      <c r="C164" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="38" t="s">
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
         <v>923</v>
       </c>
-      <c r="B164" s="38" t="s">
+      <c r="B165" t="s">
         <v>937</v>
       </c>
-      <c r="C164" s="38" t="s">
+      <c r="C165" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="38" t="s">
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
         <v>924</v>
       </c>
-      <c r="B165" s="38" t="s">
+      <c r="B166" t="s">
         <v>938</v>
       </c>
-      <c r="C165" s="38" t="s">
+      <c r="C166" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="38" t="s">
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
         <v>925</v>
       </c>
-      <c r="B166" s="38" t="s">
+      <c r="B167" t="s">
         <v>939</v>
       </c>
-      <c r="C166" s="38" t="s">
+      <c r="C167" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="38" t="s">
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
         <v>926</v>
       </c>
-      <c r="B167" s="38" t="s">
+      <c r="B168" t="s">
         <v>940</v>
       </c>
-      <c r="C167" s="38" t="s">
+      <c r="C168" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
-      <c r="A168" s="38" t="s">
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
         <v>927</v>
       </c>
-      <c r="B168" s="38" t="s">
+      <c r="B169" t="s">
         <v>941</v>
       </c>
-      <c r="C168" s="38" t="s">
+      <c r="C169" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="38" t="s">
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
         <v>928</v>
       </c>
-      <c r="B169" s="38" t="s">
+      <c r="B170" t="s">
         <v>942</v>
       </c>
-      <c r="C169" s="38" t="s">
+      <c r="C170" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="38" t="s">
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
         <v>929</v>
       </c>
-      <c r="B170" s="38" t="s">
+      <c r="B171" t="s">
         <v>943</v>
       </c>
-      <c r="C170" s="38" t="s">
+      <c r="C171" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
-      <c r="A171" s="38" t="s">
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
         <v>930</v>
       </c>
-      <c r="B171" s="38" t="s">
+      <c r="B172" t="s">
         <v>944</v>
       </c>
-      <c r="C171" s="38" t="s">
+      <c r="C172" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="38" t="s">
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
         <v>931</v>
       </c>
-      <c r="B172" s="38" t="s">
+      <c r="B173" t="s">
         <v>945</v>
       </c>
-      <c r="C172" s="38" t="s">
+      <c r="C173" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
-      <c r="A173" s="38" t="s">
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
         <v>932</v>
       </c>
-      <c r="B173" s="38" t="s">
+      <c r="B174" t="s">
         <v>946</v>
       </c>
-      <c r="C173" s="38" t="s">
+      <c r="C174" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
-      <c r="A174" s="38" t="s">
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
         <v>933</v>
       </c>
-      <c r="B174" s="38" t="s">
+      <c r="B175" t="s">
         <v>947</v>
       </c>
-      <c r="C174" s="38" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" s="38" t="s">
-        <v>934</v>
-      </c>
-      <c r="B175" s="38" t="s">
-        <v>948</v>
-      </c>
-      <c r="C175" s="39" t="s">
-        <v>948</v>
+      <c r="C175" s="8" t="s">
+        <v>947</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.5" customHeight="1">
       <c r="A176" t="s">
+        <v>961</v>
+      </c>
+      <c r="B176" t="s">
         <v>962</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
         <v>963</v>
       </c>
-      <c r="C176" t="s">
+      <c r="B177" t="s">
+        <v>964</v>
+      </c>
+      <c r="C177" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="38" t="s">
-        <v>964</v>
-      </c>
-      <c r="B177" s="38" t="s">
-        <v>965</v>
-      </c>
-      <c r="C177" s="38" t="s">
+    <row r="178" spans="1:3" ht="25">
+      <c r="A178" t="s">
         <v>967</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" ht="26.4">
-      <c r="A178" t="s">
+      <c r="B178" t="s">
         <v>968</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" s="3" t="s">
         <v>969</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
+        <v>970</v>
+      </c>
+      <c r="B179" t="s">
         <v>971</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>972</v>
-      </c>
-      <c r="C179" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
+        <v>973</v>
+      </c>
+      <c r="B180" t="s">
         <v>974</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>975</v>
-      </c>
-      <c r="C180" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
+        <v>976</v>
+      </c>
+      <c r="B181" t="s">
         <v>977</v>
       </c>
-      <c r="B181" t="s">
-        <v>978</v>
-      </c>
       <c r="C181" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
+        <v>978</v>
+      </c>
+      <c r="B182" t="s">
         <v>979</v>
       </c>
-      <c r="B182" t="s">
-        <v>980</v>
-      </c>
       <c r="C182" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
+        <v>982</v>
+      </c>
+      <c r="B183" t="s">
         <v>983</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>984</v>
-      </c>
-      <c r="C183" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
+        <v>985</v>
+      </c>
+      <c r="B184" t="s">
         <v>986</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>987</v>
-      </c>
-      <c r="C184" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B185" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C185" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B186" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C186" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B187" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C187" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
+        <v>994</v>
+      </c>
+      <c r="B188" t="s">
         <v>995</v>
       </c>
-      <c r="B188" t="s">
-        <v>996</v>
-      </c>
       <c r="C188" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
+        <v>996</v>
+      </c>
+      <c r="B189" t="s">
         <v>997</v>
       </c>
-      <c r="B189" t="s">
-        <v>998</v>
-      </c>
       <c r="C189" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
+        <v>998</v>
+      </c>
+      <c r="B190" t="s">
         <v>999</v>
       </c>
-      <c r="B190" t="s">
-        <v>1000</v>
-      </c>
       <c r="C190" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B191" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C191" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B192" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C192" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B193" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C193" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B194" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C194" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B195" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C195" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B196" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C196" s="38" t="s">
-        <v>1018</v>
+        <v>1010</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B197" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C197" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="13" t="s">
+      <c r="A198" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="B198" s="12" t="s">
+      <c r="B198" s="8" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C198" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="C198" s="12" t="s">
-        <v>630</v>
-      </c>
-      <c r="D198" s="31" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A199" s="41" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B199" s="42" t="s">
+      <c r="D198" s="5" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" s="21" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A199" s="17" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B199" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C199" s="19" t="s">
         <v>1028</v>
       </c>
-      <c r="C199" s="43" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D199" s="44" t="s">
-        <v>912</v>
+      <c r="D199" s="20" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B200" t="s">
         <v>1031</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>1032</v>
-      </c>
-      <c r="C200" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B201" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C201" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B202" t="s">
         <v>1035</v>
       </c>
-      <c r="B202" t="s">
-        <v>1036</v>
-      </c>
       <c r="C202" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B203" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C203" t="s">
         <v>1047</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B204" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C204" t="s">
         <v>1049</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B205" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C205" t="s">
         <v>1051</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B206" t="s">
         <v>1040</v>
       </c>
-      <c r="B206" t="s">
-        <v>1041</v>
-      </c>
       <c r="C206" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B207" t="s">
         <v>1042</v>
       </c>
-      <c r="B207" t="s">
-        <v>1043</v>
-      </c>
       <c r="C207" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B208" t="s">
         <v>1053</v>
       </c>
-      <c r="B208" t="s">
-        <v>1054</v>
-      </c>
       <c r="C208" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B209" t="s">
         <v>1055</v>
       </c>
-      <c r="B209" t="s">
-        <v>1056</v>
-      </c>
       <c r="C209" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B210" t="s">
         <v>1057</v>
       </c>
-      <c r="B210" t="s">
-        <v>1058</v>
-      </c>
       <c r="C210" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C211" t="s">
         <v>1063</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C211" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C212" t="s">
         <v>1066</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C212" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B213" s="39" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C213" s="39" t="s">
-        <v>1088</v>
+        <v>1067</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C213" s="8" t="s">
+        <v>1087</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B214" s="39" t="s">
-        <v>1081</v>
+        <v>1068</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>1080</v>
       </c>
       <c r="C214" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B215" s="39" t="s">
-        <v>1084</v>
+        <v>1069</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>1083</v>
       </c>
       <c r="C215" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B216" s="39" t="s">
-        <v>1082</v>
+        <v>1070</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>1081</v>
       </c>
       <c r="C216" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="B217" s="39" t="s">
+      <c r="B218" s="8" t="s">
         <v>1085</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C218" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="39" t="s">
+    <row r="219" spans="1:3">
+      <c r="A219" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="B218" s="39" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C218" t="s">
+      <c r="B219" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C219" t="s">
         <v>1093</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="39" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B219" s="39" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C219" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="B220" s="39" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C220" t="s">
+      <c r="B221" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C221" t="s">
         <v>1095</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="39" t="s">
+    <row r="222" spans="1:3">
+      <c r="A222" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="B221" s="39" t="s">
+      <c r="B222" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C222" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
-      <c r="A222" s="39" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B222" s="39" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C222" t="s">
+    <row r="223" spans="1:3">
+      <c r="A223" s="8" t="s">
         <v>1097</v>
       </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="39" t="s">
+      <c r="B223" s="8" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" s="8" t="s">
         <v>1098</v>
       </c>
-      <c r="B223" s="39" t="s">
+      <c r="B224" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C224" t="s">
         <v>1102</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="39" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B224" s="39" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C224" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B225" s="8" t="s">
         <v>1104</v>
       </c>
-      <c r="B225" s="39" t="s">
+      <c r="C225" s="8" t="s">
         <v>1105</v>
-      </c>
-      <c r="C225" s="39" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B226" s="8" t="s">
         <v>1107</v>
       </c>
-      <c r="B226" s="39" t="s">
+      <c r="C226" s="8" t="s">
         <v>1108</v>
       </c>
-      <c r="C226" s="39" t="s">
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" s="8" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="39" t="s">
+      <c r="B227" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" s="8" t="s">
         <v>1110</v>
       </c>
-      <c r="B227" s="39" t="s">
+      <c r="B228" s="8" t="s">
         <v>1118</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C228" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="39" t="s">
+    <row r="229" spans="1:3">
+      <c r="A229" s="8" t="s">
         <v>1111</v>
       </c>
-      <c r="B228" s="39" t="s">
+      <c r="B229" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C229" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="39" t="s">
+    <row r="230" spans="1:3">
+      <c r="A230" s="8" t="s">
         <v>1112</v>
       </c>
-      <c r="B229" s="39" t="s">
+      <c r="B230" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C230" t="s">
         <v>1128</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="39" t="s">
+    <row r="231" spans="1:3">
+      <c r="A231" s="8" t="s">
         <v>1113</v>
       </c>
-      <c r="B230" s="39" t="s">
+      <c r="B231" s="8" t="s">
         <v>1121</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C231" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="39" t="s">
+    <row r="232" spans="1:3">
+      <c r="A232" s="8" t="s">
         <v>1114</v>
       </c>
-      <c r="B231" s="39" t="s">
+      <c r="B232" s="8" t="s">
         <v>1122</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C232" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="39" t="s">
+    <row r="233" spans="1:3">
+      <c r="A233" s="8" t="s">
         <v>1115</v>
       </c>
-      <c r="B232" s="39" t="s">
+      <c r="B233" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C233" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="39" t="s">
+    <row r="234" spans="1:3">
+      <c r="A234" s="8" t="s">
         <v>1116</v>
       </c>
-      <c r="B233" s="39" t="s">
+      <c r="B234" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C234" t="s">
         <v>1132</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
-      <c r="A234" s="39" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B234" s="39" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C234" t="s">
+    <row r="235" spans="1:3">
+      <c r="A235" s="8" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235" s="39" t="s">
+      <c r="B235" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="B235" s="39" t="s">
+      <c r="C235" t="s">
         <v>1135</v>
       </c>
-      <c r="C235" t="s">
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" s="8" t="s">
         <v>1136</v>
       </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="39" t="s">
+      <c r="B236" s="8" t="s">
         <v>1137</v>
       </c>
-      <c r="B236" s="39" t="s">
+      <c r="C236" t="s">
         <v>1138</v>
-      </c>
-      <c r="C236" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B237" t="s">
         <v>1140</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" t="s">
         <v>1141</v>
       </c>
-      <c r="C237" t="s">
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" s="8" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="39" t="s">
+      <c r="B238" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B238" s="39" t="s">
+      <c r="C238" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="C238" t="s">
+      <c r="B239" s="8" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C239" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="39" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B239" s="39" t="s">
+    <row r="240" spans="1:3">
+      <c r="A240" s="8" t="s">
         <v>1146</v>
       </c>
-      <c r="C239" t="s">
+      <c r="B240" s="8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C240" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="39" t="s">
+    <row r="241" spans="1:3">
+      <c r="A241" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="B240" s="39" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C240" t="s">
+      <c r="B241" s="8" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C241" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="39" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B241" s="39" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C241" t="s">
-        <v>1154</v>
+    <row r="242" spans="1:3">
+      <c r="A242" s="9" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C242" s="8"/>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="8" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="8" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="8" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
